--- a/data/quotas/quota_onnuri_서울_풍납시장_온누리쿼터_개선검증_1791810270551.xlsx
+++ b/data/quotas/quota_onnuri_서울_풍납시장_온누리쿼터_개선검증_1791810270551.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -405,10 +405,12 @@
     <col min="4" max="4" width="19.234375" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="44.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="44.83203125" customWidth="1"/>
+    <col min="11" max="11" width="45.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,18 +430,24 @@
         <v>대표자명</v>
       </c>
       <c r="F1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="G1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="H1" t="str">
         <v>연락처</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>개업연월</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>취급품목</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>주소</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>가맹상태</v>
       </c>
     </row>
@@ -463,15 +471,21 @@
         <v/>
       </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>2020.10.06</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>수산물 (신선)</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -495,15 +509,21 @@
         <v/>
       </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>2012.03.13</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>기타소매업 (두발 미용업)</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>서울특별시 송파구 풍납동 87-4 예작헤어라인</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -527,15 +547,21 @@
         <v/>
       </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>2023.10.06</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>기타소매업 (피부 미용업)</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>서울특별시 송파구 풍납동 2층 201호</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -559,15 +585,21 @@
         <v/>
       </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>2025.06.11</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>농산물 (곡물)</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>서울특별시 송파구 풍납동 1층 4호</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -591,21 +623,27 @@
         <v/>
       </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>2022.03.14</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>수산물 (음ㆍ식료품 및 담배 도매업 외 1개)</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>서울특별시 송파구 풍납동 149-12 1층</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>정상가맹</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>